--- a/artfynd/A 48628-2023 artfynd.xlsx
+++ b/artfynd/A 48628-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48628-2023 artfynd.xlsx
+++ b/artfynd/A 48628-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17042912</v>
+        <v>442337</v>
       </c>
       <c r="B2" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223246</v>
+        <v>1468</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Brunskaftad blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Sclerophora farinacea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Chevall.) Chevall.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ekhage vid Hulebo, Ög</t>
+          <t>(07G6b02), Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554026.5057264651</v>
+        <v>554009</v>
       </c>
       <c r="R2" t="n">
-        <v>6429210.507241572</v>
+        <v>6429291</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1969-06-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-05-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1969-07-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-05-17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Äldre uppgifter om Östergötlands flora. Referens: Wennerbo, Birgit 1970. Vegetationen i Nedre Emmern. Växtbiol. Inst. Uppsala Universitet (stencil), 15 + 13 s. Inlagda i Artportalen av Tommy Tyrberg.</t>
+          <t>070661021 / SCL FARI / Tämligen allmän (2)  / OBJ.AREA:0,1 ha</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,69 +762,77 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AR2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Hamlat träd</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Tyrberg</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Tommy Tyrberg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Tommy Ek</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17042910</v>
+        <v>838349</v>
       </c>
       <c r="B3" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ekhage vid Hulebo, Ög</t>
+          <t>(07G6b04), Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554026.5057264651</v>
+        <v>554123</v>
       </c>
       <c r="R3" t="n">
-        <v>6429210.507241572</v>
+        <v>6429313</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,27 +856,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1969-06-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-05-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1969-07-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-05-17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre uppgifter om Östergötlands flora. Referens: Wennerbo, Birgit 1970. Vegetationen i Nedre Emmern. Växtbiol. Inst. Uppsala Universitet (stencil), 15 + 13 s. Inlagda i Artportalen av Tommy Tyrberg.</t>
+          <t>070661041 / ANTI CUR / Enstaka-sparsam (1)  / OBJ.AREA:0,2 ha</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,19 +878,835 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AR3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Hamlat träd</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tommy Tyrberg</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Tommy Tyrberg</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Tommy Ek</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>673843</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96231</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>(07G6b04), Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>554123</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6429313</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1995-05-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1995-05-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>070661041 / HOMA SER / Tämligen allmän (2)  / OBJ.AREA:0,2 ha</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Hamlat träd</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tommy Ek</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>673844</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96231</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>(07G6b03), Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>554064</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6429348</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1995-05-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1995-05-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>070661031 / HOMA SER / Allmän-riklig (3)  / OBJ.AREA:0,1 ha</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Hamlat träd</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tommy Ek</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1995929</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79707</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>(07G6b04), Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>554123</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6429313</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>1995-05-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1995-05-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>070661041 / BAC RUBE / Enstaka-sparsam (1)  / OBJ.AREA:0,2 ha</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Hamlat träd</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tommy Ek</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1995930</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79707</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>(07G6b03), Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>554064</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6429348</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1995-05-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1995-05-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>070661031 / BAC RUBE / Allmän-riklig (3)  / OBJ.AREA:0,1 ha</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Hamlat träd</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tommy Ek</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2064663</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80358</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6455</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>(07G6b03), Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>554064</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6429348</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>1995-05-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1995-05-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>070661031 / LEP LICH / Allmän-riklig (3)  / OBJ.AREA:0,1 ha</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Hamlat träd</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tommy Ek</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2037178</v>
+      </c>
+      <c r="B9" t="n">
+        <v>83314</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6471</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gulvit blekspik</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sclerophora pallida</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>(07G6b02), Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>554009</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6429291</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>1995-05-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1995-05-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>070661021 / SCL NIVE / Tämligen allmän (2)  / OBJ.AREA:0,1 ha</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Hamlat träd</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tommy Ek</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2037179</v>
+      </c>
+      <c r="B10" t="n">
+        <v>83314</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6471</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gulvit blekspik</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sclerophora pallida</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>(07G6b04), Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>554123</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6429313</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>1995-05-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1995-05-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>070661041 / SCL NIVE / Enstaka-sparsam (1)  / OBJ.AREA:0,2 ha</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Hamlat träd</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tommy Ek</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48628-2023 artfynd.xlsx
+++ b/artfynd/A 48628-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/442337</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/838349</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/673843</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/673844</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1995929</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1995930</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1475,6 +1510,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2064663</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1591,6 +1631,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2037178</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1707,8 +1752,24 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2037179</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>